--- a/Extra/testcases.xlsx
+++ b/Extra/testcases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2e15cca3989f5e5d/Documents/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{17693E5E-55DB-472C-B54D-CEC48918FABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E586C265-9FD1-4296-BC0D-3667F2A646A7}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{17693E5E-55DB-472C-B54D-CEC48918FABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59DAEC88-C85E-49D8-9D03-FD0F91785379}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tong quan" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,250 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="23">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="15"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="16"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="17"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="18"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="19"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="20"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="21"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="23">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
+    </bk>
+    <bk>
+      <rc t="1" v="8"/>
+    </bk>
+    <bk>
+      <rc t="1" v="9"/>
+    </bk>
+    <bk>
+      <rc t="1" v="10"/>
+    </bk>
+    <bk>
+      <rc t="1" v="11"/>
+    </bk>
+    <bk>
+      <rc t="1" v="12"/>
+    </bk>
+    <bk>
+      <rc t="1" v="13"/>
+    </bk>
+    <bk>
+      <rc t="1" v="14"/>
+    </bk>
+    <bk>
+      <rc t="1" v="15"/>
+    </bk>
+    <bk>
+      <rc t="1" v="16"/>
+    </bk>
+    <bk>
+      <rc t="1" v="17"/>
+    </bk>
+    <bk>
+      <rc t="1" v="18"/>
+    </bk>
+    <bk>
+      <rc t="1" v="19"/>
+    </bk>
+    <bk>
+      <rc t="1" v="20"/>
+    </bk>
+    <bk>
+      <rc t="1" v="21"/>
+    </bk>
+    <bk>
+      <rc t="1" v="22"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="142">
   <si>
     <t>Bang test case du an TCP Chat GUI</t>
   </si>
@@ -118,12 +360,6 @@
     <t>Đăng nhập thành công và mở được màn hình chat Lobby.</t>
   </si>
   <si>
-    <t>Chưa test</t>
-  </si>
-  <si>
-    <t>Ảnh màn hình đăng nhập và Lobby</t>
-  </si>
-  <si>
     <t>TC_02</t>
   </si>
   <si>
@@ -139,9 +375,6 @@
     <t>Client thứ hai bị từ chối và hiển thị thông báo lỗi.</t>
   </si>
   <si>
-    <t>Ảnh thông báo lỗi đăng nhập trùng</t>
-  </si>
-  <si>
     <t>TC_03</t>
   </si>
   <si>
@@ -157,9 +390,6 @@
     <t>Tất cả user đang ở Lobby đều nhìn thấy đúng 1 tin nhắn với đúng người gửi.</t>
   </si>
   <si>
-    <t>Ảnh chụp từ 3 client</t>
-  </si>
-  <si>
     <t>TC_04</t>
   </si>
   <si>
@@ -175,9 +405,6 @@
     <t>Chỉ An và Binh thấy tin nhắn riêng; Chi không nhìn thấy.</t>
   </si>
   <si>
-    <t>Ảnh sender, receiver và client thứ ba</t>
-  </si>
-  <si>
     <t>TC_05</t>
   </si>
   <si>
@@ -193,9 +420,6 @@
     <t>Conversation group mới xuất hiện với đúng các thành viên đã chọn.</t>
   </si>
   <si>
-    <t>Ảnh tạo group và danh sách thành viên</t>
-  </si>
-  <si>
     <t>TC_06</t>
   </si>
   <si>
@@ -211,9 +435,6 @@
     <t>Chỉ các thành viên của group nhận được tin nhắn trong conversation đó.</t>
   </si>
   <si>
-    <t>Ảnh từ các thành viên group</t>
-  </si>
-  <si>
     <t>TC_07</t>
   </si>
   <si>
@@ -229,9 +450,6 @@
     <t>Danh sách online thêm Chi khi login và xóa Chi khi logout/disconnect.</t>
   </si>
   <si>
-    <t>Ảnh trước và sau khi thay đổi</t>
-  </si>
-  <si>
     <t>TC_08</t>
   </si>
   <si>
@@ -247,9 +465,6 @@
     <t>Các user khác nhận được thông báo join và leave phù hợp.</t>
   </si>
   <si>
-    <t>Ảnh chụp hoặc log client/server</t>
-  </si>
-  <si>
     <t>TC_09</t>
   </si>
   <si>
@@ -259,15 +474,9 @@
     <t>Kiểm tra file dưới 10MB có thể được gửi lên.</t>
   </si>
   <si>
-    <t>An gửi một file PDF 1MB trong Lobby.</t>
-  </si>
-  <si>
     <t>File được upload, xuất hiện trong chat và metadata được lưu nếu có cấu hình DB.</t>
   </si>
   <si>
-    <t>Ảnh chat và thư mục server_files</t>
-  </si>
-  <si>
     <t>TC_10</t>
   </si>
   <si>
@@ -283,9 +492,6 @@
     <t>File được tải thành công vào thư mục downloads và mở được.</t>
   </si>
   <si>
-    <t>Ảnh màn hình và thư mục downloads</t>
-  </si>
-  <si>
     <t>TC_11</t>
   </si>
   <si>
@@ -301,9 +507,6 @@
     <t>Các conversation cũ và tin nhắn gần nhất được tải lại.</t>
   </si>
   <si>
-    <t>Ảnh trước khi đóng và sau khi đăng nhập lại</t>
-  </si>
-  <si>
     <t>TC_12</t>
   </si>
   <si>
@@ -319,9 +522,6 @@
     <t>Client hiển thị trạng thái reconnecting và kết nối lại mà không treo giao diện.</t>
   </si>
   <si>
-    <t>Video hoặc ảnh theo từng bước</t>
-  </si>
-  <si>
     <t>PT_01</t>
   </si>
   <si>
@@ -337,9 +537,6 @@
     <t>Mỗi lần đăng nhập hoàn tất trong dưới 2 giây, không treo UI.</t>
   </si>
   <si>
-    <t>Ảnh thời gian hoặc video</t>
-  </si>
-  <si>
     <t>PT_02</t>
   </si>
   <si>
@@ -355,9 +552,6 @@
     <t>Độ trễ trung bình dưới 1 giây và không mất tin nhắn.</t>
   </si>
   <si>
-    <t>Log thời gian hoặc video màn hình</t>
-  </si>
-  <si>
     <t>PT_03</t>
   </si>
   <si>
@@ -373,9 +567,6 @@
     <t>Server vẫn ổn định, tin nhắn đến đúng thứ tự và không trễ lớn.</t>
   </si>
   <si>
-    <t>Log server và ảnh Task Manager</t>
-  </si>
-  <si>
     <t>PT_04</t>
   </si>
   <si>
@@ -391,9 +582,6 @@
     <t>CPU/RAM server ở mức chấp nhận được và không bị crash.</t>
   </si>
   <si>
-    <t>Ảnh Task Manager và log</t>
-  </si>
-  <si>
     <t>PT_05</t>
   </si>
   <si>
@@ -409,9 +597,6 @@
     <t>Danh sách conversation và tin nhắn gần nhất hiện trong dưới 3 giây.</t>
   </si>
   <si>
-    <t>Video hoặc ảnh kèm mốc thời gian</t>
-  </si>
-  <si>
     <t>ST_01</t>
   </si>
   <si>
@@ -442,9 +627,6 @@
     <t>Server vẫn phản hồi, client khác vẫn nhận được tin và không bị crash.</t>
   </si>
   <si>
-    <t>Log client/server</t>
-  </si>
-  <si>
     <t>ST_03</t>
   </si>
   <si>
@@ -454,15 +636,9 @@
     <t>Kiểm tra hệ thống dưới tải nhắn tin rất cao từ nhiều client.</t>
   </si>
   <si>
-    <t>10 client, mỗi client gửi 200 tin nhắn nhanh vào Lobby hoặc group.</t>
-  </si>
-  <si>
     <t>Server vẫn sống, vẫn route được tin và không mất tin nghiêm trọng.</t>
   </si>
   <si>
-    <t>Log và ảnh màn hình</t>
-  </si>
-  <si>
     <t>ST_04</t>
   </si>
   <si>
@@ -478,9 +654,6 @@
     <t>Hệ thống dọn session cũ đúng cách và không sinh user trùng.</t>
   </si>
   <si>
-    <t>Ảnh user list và log</t>
-  </si>
-  <si>
     <t>ST_05</t>
   </si>
   <si>
@@ -496,9 +669,6 @@
     <t>Upload bị chặn, có thông báo lỗi rõ ràng và server không crash.</t>
   </si>
   <si>
-    <t>Ảnh thông báo lỗi</t>
-  </si>
-  <si>
     <t>ST_06</t>
   </si>
   <si>
@@ -514,7 +684,13 @@
     <t>Server từ chối dữ liệu lỗi mà không crash và vẫn phục vụ client hợp lệ.</t>
   </si>
   <si>
-    <t>Log server hoặc custom client proof</t>
+    <t>Đạt</t>
+  </si>
+  <si>
+    <t>An gửi một file TXT 1MB trong Lobby.</t>
+  </si>
+  <si>
+    <t>5 client, mỗi client gửi 200 tin nhắn nhanh vào Lobby hoặc group.</t>
   </si>
 </sst>
 </file>
@@ -764,10 +940,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -885,6 +1061,184 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="23">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>8</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>9</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>10</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>11</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>12</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>13</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>14</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>15</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>16</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>17</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>18</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>19</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>20</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>21</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>22</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
+  <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
+  <rel r:id="rId11"/>
+  <rel r:id="rId12"/>
+  <rel r:id="rId13"/>
+  <rel r:id="rId14"/>
+  <rel r:id="rId15"/>
+  <rel r:id="rId16"/>
+  <rel r:id="rId17"/>
+  <rel r:id="rId18"/>
+  <rel r:id="rId19"/>
+  <rel r:id="rId20"/>
+  <rel r:id="rId21"/>
+  <rel r:id="rId22"/>
+  <rel r:id="rId23"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1083,21 +1437,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:G13"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="28.05" customHeight="1">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:7" ht="28.15" customHeight="1">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="4" spans="2:7" ht="24" customHeight="1">
       <c r="B4" s="2" t="s">
@@ -1183,7 +1537,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:H14"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
@@ -1193,16 +1547,16 @@
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="25.95" customHeight="1">
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="2:8" ht="25.9" customHeight="1">
+      <c r="B1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="2:8" ht="24" customHeight="1">
       <c r="B2" s="5" t="s">
@@ -1227,7 +1581,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="43.95" customHeight="1">
+    <row r="3" spans="2:8" ht="43.9" customHeight="1">
       <c r="B3" s="8" t="s">
         <v>26</v>
       </c>
@@ -1244,263 +1598,263 @@
         <v>30</v>
       </c>
       <c r="G3" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="10" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="G4" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="10" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="G5" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="10" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B6" s="8" t="s">
+      <c r="F6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="G6" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="10" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B7" s="8" t="s">
+      <c r="G7" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="10" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="G8" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="10" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B9" s="8" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B8" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="10" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B9" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="G10" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10" s="10" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="C11" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="10" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B10" s="8" t="s">
+      <c r="E11" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="G11" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="10" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B12" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B11" s="8" t="s">
+      <c r="G12" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H12" s="10" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B13" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="G13" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="10" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B14" s="11" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B12" s="8" t="s">
+      <c r="C14" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D14" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E14" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F14" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B13" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B14" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>97</v>
-      </c>
       <c r="G14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>98</v>
+        <v>139</v>
+      </c>
+      <c r="H14" s="13" t="e" vm="12">
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1524,7 +1878,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:H7"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
@@ -1534,16 +1888,16 @@
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="25.95" customHeight="1">
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="2:8" ht="25.9" customHeight="1">
+      <c r="B1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="2:8" ht="24" customHeight="1">
       <c r="B2" s="5" t="s">
@@ -1568,119 +1922,119 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="43.95" customHeight="1">
+    <row r="3" spans="2:8" ht="43.9" customHeight="1">
       <c r="B3" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="10" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B4" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="10" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B5" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="G5" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="10" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B6" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B4" s="8" t="s">
+      <c r="G6" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="10" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B7" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C7" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E7" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F7" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B5" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B7" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>127</v>
-      </c>
       <c r="G7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>128</v>
+        <v>139</v>
+      </c>
+      <c r="H7" s="13" t="e" vm="17">
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1704,7 +2058,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:H8"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
@@ -1714,16 +2068,16 @@
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="25.95" customHeight="1">
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="2:8" ht="25.9" customHeight="1">
+      <c r="B1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="2:8" ht="24" customHeight="1">
       <c r="B2" s="5" t="s">
@@ -1748,142 +2102,142 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="43.95" customHeight="1">
+    <row r="3" spans="2:8" ht="43.9" customHeight="1">
       <c r="B3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="10" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B4" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="10" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B5" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="10" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B6" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="10" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B7" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B4" s="8" t="s">
+      <c r="G7" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="10" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="43.9" customHeight="1">
+      <c r="B8" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C8" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E8" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F8" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="10" t="s">
+      <c r="G8" s="9" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B5" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B6" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B7" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="43.95" customHeight="1">
-      <c r="B8" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>163</v>
+      <c r="H8" s="13" t="e" vm="23">
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
